--- a/GameConfig/Datas/通用/功能参数配置表.xlsx
+++ b/GameConfig/Datas/通用/功能参数配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\通用\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE1A64D-EE5B-4FD8-8D08-FED9DD83B324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3305571D-411A-41B3-9DA4-E42F75E354DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="功能参数配置表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>##column#var</t>
   </si>
@@ -125,6 +125,22 @@
   </si>
   <si>
     <t>记录服务器最近登录最大个数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OldSessionLifeTime</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>断线重连时旧的Session生命周期(毫秒)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DelayOfflineTime</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>延迟下线时间(毫秒)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -507,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="59.1640625" customWidth="1"/>
@@ -719,11 +735,19 @@
       <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="5"/>
+      <c r="A10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3000</v>
+      </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="10" t="s">
+        <v>28</v>
+      </c>
       <c r="F10" s="5"/>
       <c r="G10" s="6"/>
       <c r="H10" s="5"/>
@@ -732,6 +756,20 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
     </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="5">
+        <v>5000</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GameConfig/Datas/通用/功能参数配置表.xlsx
+++ b/GameConfig/Datas/通用/功能参数配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\通用\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3305571D-411A-41B3-9DA4-E42F75E354DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB6AE77-0D88-4589-B35E-CD6E1E9C6F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="功能参数配置表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>##column#var</t>
   </si>
@@ -141,6 +141,14 @@
   </si>
   <si>
     <t>延迟下线时间(毫秒)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerInitConfigID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家创建账号的初始角色配置ID</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -523,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="59.1640625" customWidth="1"/>
@@ -770,6 +778,20 @@
         <v>30</v>
       </c>
     </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GameConfig/Datas/通用/功能参数配置表.xlsx
+++ b/GameConfig/Datas/通用/功能参数配置表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\通用\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB6AE77-0D88-4589-B35E-CD6E1E9C6F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE3A5DC-CC19-4E45-9D03-050B6EC9B4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
   <si>
     <t>##column#var</t>
   </si>
@@ -149,6 +149,70 @@
   </si>
   <si>
     <t>玩家创建账号的初始角色配置ID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleNameChineseMinCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleNameChineseMaxCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯中文模式下最少字符数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯中文模式下最多字符数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleNameLatinMinCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleNameLatinMaxCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯英文模式下最少字符数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯英文模式下最多字符数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleNameMixedMinCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleNameMixedMaxCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>混排模式下最少字符数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>混排模式下最多字符数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleNameDigitMinCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleNameDigitMaxCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯数字模式下最少字符数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯数字模式下最多字符数</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -226,12 +290,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -531,265 +591,330 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="59.1640625" customWidth="1"/>
-    <col min="2" max="2" width="11.75" customWidth="1"/>
-    <col min="3" max="3" width="58.58203125" customWidth="1"/>
-    <col min="4" max="4" width="10.58203125" customWidth="1"/>
-    <col min="5" max="5" width="38.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12.4140625" customWidth="1"/>
-    <col min="9" max="9" width="17.9140625" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" customWidth="1"/>
+    <col min="1" max="1" width="59.1640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="4" customWidth="1"/>
+    <col min="3" max="3" width="58.58203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.58203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="38.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="12.4140625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="17.9140625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="28" style="4" customWidth="1"/>
+    <col min="11" max="11" width="13" style="4" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="4" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="2" t="s">
+      <c r="F1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="F2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="F3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="F4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>300000</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="F5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="F6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="F7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="3">
         <v>2000</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="F8" s="6"/>
+      <c r="H8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="B9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3">
         <v>4</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="F9" s="6"/>
+      <c r="H9" s="3"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="B10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="3">
         <v>3000</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="F10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="5">
+      <c r="B11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="3">
         <v>5000</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="5">
+      <c r="B12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3">
         <v>1</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="8" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="3">
+        <v>6</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="3">
+        <v>12</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="3">
+        <v>4</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="3">
+        <v>12</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="3">
+        <v>4</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="3">
+        <v>12</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/通用/功能参数配置表.xlsx
+++ b/GameConfig/Datas/通用/功能参数配置表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\通用\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE3A5DC-CC19-4E45-9D03-050B6EC9B4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9387856-AF48-4EAE-AF7A-4C3C60EDBCA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
   <si>
     <t>##column#var</t>
   </si>
@@ -213,6 +213,26 @@
   </si>
   <si>
     <t>纯数字模式下最多字符数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>AuthenticationAddress</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>AuthenticationPort</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>127.0.0.1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>鉴权服务器地址</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>鉴权服务器端口号</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -591,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="59.1640625" style="4" customWidth="1"/>
@@ -917,6 +937,34 @@
         <v>48</v>
       </c>
     </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="4">
+        <v>20001</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GameConfig/Datas/通用/功能参数配置表.xlsx
+++ b/GameConfig/Datas/通用/功能参数配置表.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\通用\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9387856-AF48-4EAE-AF7A-4C3C60EDBCA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="功能参数配置表" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
   <si>
     <t>##column#var</t>
   </si>
@@ -59,12 +53,18 @@
     <t>string</t>
   </si>
   <si>
+    <t>MIIBCgKCAQEA0PxKWKHSqRbF5wMgwOEX2BFu+8tg5Ml0MnZr4ZnfajoPemXRD1eN/rzfFRVkr+uHttwr/pCeJqIB0I2ZbHQ9Hs8t/c+MqrC2/MCmqWn5uLFpFASvPid8qGtoBCAWyVMkoJbQR3t05tfHmRQHpclKjJkv9BqhkNk5NeDRoQxU/4kSMVj2DSGLXF0RFrcPrp8ijR9oP/TMdUbUMbXH1NIal1kwHBYyFkXk1FxBgiWfWWyx2O/CLvJHaNpcXvv/JQ96gXMJ2QSoJt3I4mkxA/0WJO603wLg02NlqrwFMorJ7fTWqZcTLcsUjxCWIFPYoHknjX6NJEgpS+1n13sLA+GaUQIDAQAB</t>
+  </si>
+  <si>
     <t>账号Token公钥</t>
   </si>
   <si>
     <t>AccountTokenPrivateKeyPem</t>
   </si>
   <si>
+    <t>MIIEowIBAAKCAQEA0PxKWKHSqRbF5wMgwOEX2BFu+8tg5Ml0MnZr4ZnfajoPemXRD1eN/rzfFRVkr+uHttwr/pCeJqIB0I2ZbHQ9Hs8t/c+MqrC2/MCmqWn5uLFpFASvPid8qGtoBCAWyVMkoJbQR3t05tfHmRQHpclKjJkv9BqhkNk5NeDRoQxU/4kSMVj2DSGLXF0RFrcPrp8ijR9oP/TMdUbUMbXH1NIal1kwHBYyFkXk1FxBgiWfWWyx2O/CLvJHaNpcXvv/JQ96gXMJ2QSoJt3I4mkxA/0WJO603wLg02NlqrwFMorJ7fTWqZcTLcsUjxCWIFPYoHknjX6NJEgpS+1n13sLA+GaUQIDAQABAoIBAGCdYlmbZmKZjqCAB7Jj3bwcQyzRF1ht8fQqXzGLC4h2kxVI4N+w4Ip2EsQSgdv6jWFyZDxp61N87k3WSKmlC2Sk72Q5gZSf4djzz5jez34dNrD0gXfAlZbfINVXaHFmqLY9QsjpQGBAPZx9cBOq/XYGk+7MKQloA1TvPLqxktIXXBmxokMtLnxSbRoI1jueHYhKDVvLO2UYXxq9IdjoKKaMLNVsrmf2U8rDG7XZfduopicffogY6TeX3cdxyg8Uzkm1nLWO9nJtHL62KnFyXHTXjumLKAaIf+WcbvfJ+s9cY18pFL8sPeq4xbRW2w06Zp230QBe9uuFusbmezrLbSkCgYEA18SW8o/7oVvjzJGLE0184omdcD4wL7ZXJXnjdPR0vasCOnUmHWkiL4u+wWR/BA8GsfDT+805xfgmMis/3zLuLDul0rYlAvMa2MLb+IdpIwT+TlAH5b4dE8hOWKcocyEVzNfZQQYf4ziWQnrXEqxMYYaQe7v8blONgWT5WUf8rGcCgYEA9/PzV3PBzvN4h2sulgT/oa904AuzFAPNBXeWU/l57PrDqG2NttlF4S1zhRNzXzSlODt5KR/44QQAYj6Nwje6nfaMDM/NRrnkGbZzRW80RP1DOUb9q903h58rGs6qy8vY4YlPM75QLva9g0ZXptengskk7q3EYH1p1YsMyYiZ0IcCgYBwz5dAYSll9x5GQb5eLEBkTSEko08cUxCDRpQ2/Ozgkb2LhN6Vt/cotr7YbEvAen68oDalS2quaAzIZDZz4zQFqnYLkjINtb9On6rU6S9+IMk5drx6UQjw4+Sak2MhtqWoQR6U0bfwXBCr14AFglI5F1sJZoMXx9WPVpTMKkggdwKBgQDQXA+AzaVvYulF4qujJVArbmWoYCx8BTWkAnow1tO+cHs6bdVIcgxmzOrmSRIKTxMHzfJivJtHezVXWXmGW45Wb3gAzB6T8GHduZPkJS6nSqvS1fUVFzAyp25xeHnOB96Yp+oGcUawMGfQiKvfaBk7rgt7BkqfSsREzjRQppmawQKBgDPS3KrmXgNViKbhYxt9dt4O95cfLw34fNOwpg33G6N0iEonykpn3JomkMG0YVgEsS0u/5/6qsMHFOvpDWSI2QrpZZPVH7pxbvAMED0UpD9CThRUGrvQ+MWHitKt1SjaesY2SSIRcrgu2TjwzM3VfF29anXmW3mXw2titgUVJZkG</t>
+  </si>
+  <si>
     <t>账号Token私钥</t>
   </si>
   <si>
@@ -77,170 +77,143 @@
     <t>账号Token过期时间(毫秒)</t>
   </si>
   <si>
-    <t>MIIEowIBAAKCAQEA0PxKWKHSqRbF5wMgwOEX2BFu+8tg5Ml0MnZr4ZnfajoPemXRD1eN/rzfFRVkr+uHttwr/pCeJqIB0I2ZbHQ9Hs8t/c+MqrC2/MCmqWn5uLFpFASvPid8qGtoBCAWyVMkoJbQR3t05tfHmRQHpclKjJkv9BqhkNk5NeDRoQxU/4kSMVj2DSGLXF0RFrcPrp8ijR9oP/TMdUbUMbXH1NIal1kwHBYyFkXk1FxBgiWfWWyx2O/CLvJHaNpcXvv/JQ96gXMJ2QSoJt3I4mkxA/0WJO603wLg02NlqrwFMorJ7fTWqZcTLcsUjxCWIFPYoHknjX6NJEgpS+1n13sLA+GaUQIDAQABAoIBAGCdYlmbZmKZjqCAB7Jj3bwcQyzRF1ht8fQqXzGLC4h2kxVI4N+w4Ip2EsQSgdv6jWFyZDxp61N87k3WSKmlC2Sk72Q5gZSf4djzz5jez34dNrD0gXfAlZbfINVXaHFmqLY9QsjpQGBAPZx9cBOq/XYGk+7MKQloA1TvPLqxktIXXBmxokMtLnxSbRoI1jueHYhKDVvLO2UYXxq9IdjoKKaMLNVsrmf2U8rDG7XZfduopicffogY6TeX3cdxyg8Uzkm1nLWO9nJtHL62KnFyXHTXjumLKAaIf+WcbvfJ+s9cY18pFL8sPeq4xbRW2w06Zp230QBe9uuFusbmezrLbSkCgYEA18SW8o/7oVvjzJGLE0184omdcD4wL7ZXJXnjdPR0vasCOnUmHWkiL4u+wWR/BA8GsfDT+805xfgmMis/3zLuLDul0rYlAvMa2MLb+IdpIwT+TlAH5b4dE8hOWKcocyEVzNfZQQYf4ziWQnrXEqxMYYaQe7v8blONgWT5WUf8rGcCgYEA9/PzV3PBzvN4h2sulgT/oa904AuzFAPNBXeWU/l57PrDqG2NttlF4S1zhRNzXzSlODt5KR/44QQAYj6Nwje6nfaMDM/NRrnkGbZzRW80RP1DOUb9q903h58rGs6qy8vY4YlPM75QLva9g0ZXptengskk7q3EYH1p1YsMyYiZ0IcCgYBwz5dAYSll9x5GQb5eLEBkTSEko08cUxCDRpQ2/Ozgkb2LhN6Vt/cotr7YbEvAen68oDalS2quaAzIZDZz4zQFqnYLkjINtb9On6rU6S9+IMk5drx6UQjw4+Sak2MhtqWoQR6U0bfwXBCr14AFglI5F1sJZoMXx9WPVpTMKkggdwKBgQDQXA+AzaVvYulF4qujJVArbmWoYCx8BTWkAnow1tO+cHs6bdVIcgxmzOrmSRIKTxMHzfJivJtHezVXWXmGW45Wb3gAzB6T8GHduZPkJS6nSqvS1fUVFzAyp25xeHnOB96Yp+oGcUawMGfQiKvfaBk7rgt7BkqfSsREzjRQppmawQKBgDPS3KrmXgNViKbhYxt9dt4O95cfLw34fNOwpg33G6N0iEonykpn3JomkMG0YVgEsS0u/5/6qsMHFOvpDWSI2QrpZZPVH7pxbvAMED0UpD9CThRUGrvQ+MWHitKt1SjaesY2SSIRcrgu2TjwzM3VfF29anXmW3mXw2titgUVJZkG</t>
-  </si>
-  <si>
-    <t>MIIBCgKCAQEA0PxKWKHSqRbF5wMgwOEX2BFu+8tg5Ml0MnZr4ZnfajoPemXRD1eN/rzfFRVkr+uHttwr/pCeJqIB0I2ZbHQ9Hs8t/c+MqrC2/MCmqWn5uLFpFASvPid8qGtoBCAWyVMkoJbQR3t05tfHmRQHpclKjJkv9BqhkNk5NeDRoQxU/4kSMVj2DSGLXF0RFrcPrp8ijR9oP/TMdUbUMbXH1NIal1kwHBYyFkXk1FxBgiWfWWyx2O/CLvJHaNpcXvv/JQ96gXMJ2QSoJt3I4mkxA/0WJO603wLg02NlqrwFMorJ7fTWqZcTLcsUjxCWIFPYoHknjX6NJEgpS+1n13sLA+GaUQIDAQAB</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>AccountValidIssuer</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fantasy</t>
+  </si>
+  <si>
+    <t>发证者</t>
   </si>
   <si>
     <t>AccountValidAudience</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>发证者</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>受众</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fantasy</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>AccountRegisterSessionLifeTime</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>注册Session的延迟销毁时间(毫秒)(短链接)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>RecentServerMaxCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>记录服务器最近登录最大个数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>OldSessionLifeTime</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>断线重连时旧的Session生命周期(毫秒)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DelayOfflineTime</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>延迟下线时间(毫秒)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>PlayerInitConfigID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>玩家创建账号的初始角色配置ID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>RoleNameChineseMinCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯中文模式下最少字符数</t>
   </si>
   <si>
     <t>RoleNameChineseMaxCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>纯中文模式下最少字符数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>纯中文模式下最多字符数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>RoleNameLatinMinCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯英文模式下最少字符数</t>
   </si>
   <si>
     <t>RoleNameLatinMaxCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>纯英文模式下最少字符数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>纯英文模式下最多字符数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>RoleNameMixedMinCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>混排模式下最少字符数</t>
   </si>
   <si>
     <t>RoleNameMixedMaxCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>混排模式下最少字符数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>混排模式下最多字符数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>RoleNameDigitMinCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯数字模式下最少字符数</t>
   </si>
   <si>
     <t>RoleNameDigitMaxCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>纯数字模式下最少字符数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>纯数字模式下最多字符数</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>AuthenticationAddress</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>127.0.0.1</t>
+  </si>
+  <si>
+    <t>鉴权服务器地址</t>
   </si>
   <si>
     <t>AuthenticationPort</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>127.0.0.1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>鉴权服务器地址</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>鉴权服务器端口号</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DefaultMaleModelID</t>
+  </si>
+  <si>
+    <t>男角色默认模型ID</t>
+  </si>
+  <si>
+    <t>DefaultFemaleModelID</t>
+  </si>
+  <si>
+    <t>女角色默认模型ID</t>
+  </si>
+  <si>
+    <t>DefaultGunFashionID</t>
+  </si>
+  <si>
+    <t>默认武器ID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,29 +229,151 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,7 +382,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,8 +392,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -306,48 +581,328 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -605,369 +1160,411 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="59.1640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="11.75" style="4" customWidth="1"/>
-    <col min="3" max="3" width="58.58203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.58203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="38.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="12.4140625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="17.9140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="28" style="4" customWidth="1"/>
-    <col min="11" max="11" width="13" style="4" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="59.1666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="58.5833333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5833333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="38.6666666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.4166666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.9166666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.16666666666667" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="J1" s="3"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="F1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="F2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1">
+        <v>300000</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="F5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="H8" s="4"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="4">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="H9" s="4"/>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="4">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4">
         <v>12</v>
       </c>
-      <c r="C5" s="4">
-        <v>300000</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="J6" s="3"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="H8" s="3"/>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="E16" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4">
         <v>4</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="H9" s="3"/>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="3">
-        <v>3000</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="3">
-        <v>5000</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="3">
-        <v>2</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="3">
-        <v>6</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="3">
+      <c r="E17" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4">
+        <v>12</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4">
         <v>4</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="E19" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="4">
         <v>12</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="3">
-        <v>4</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="3">
-        <v>12</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="3">
-        <v>4</v>
-      </c>
-      <c r="E19" s="8" t="s">
+      <c r="E20" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="3">
-        <v>12</v>
-      </c>
-      <c r="E20" s="8" t="s">
+      <c r="B21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="E21" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="7" t="s">
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1">
+        <v>20001</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="8" t="s">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="4">
-        <v>20001</v>
-      </c>
-      <c r="E22" s="8" t="s">
+      <c r="B23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="1">
+        <v>11000</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>53</v>
       </c>
     </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="1">
+        <v>21000</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="1">
+        <v>72000</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>